--- a/docs/build/lakeshore-enterprise-context/source/12_ai_use_cases_moves/procurement_vendor_optimization_use_cases.xlsx
+++ b/docs/build/lakeshore-enterprise-context/source/12_ai_use_cases_moves/procurement_vendor_optimization_use_cases.xlsx
@@ -437,7 +437,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -485,11 +485,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Spend optimization agent</t>
+          <t>FX hedge advisor</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6.5</v>
+        <v>1</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -498,7 +498,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -510,11 +510,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Vendor scorecard agent</t>
+          <t>Close acceleration assistant</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -535,15 +535,15 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Audit evidence assembler</t>
+          <t>Spend optimization agent</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.5</v>
+        <v>6.9</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6m</t>
+          <t>12m</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -560,11 +560,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cash forecasting copilot</t>
+          <t>SoD conflict detector</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -585,11 +585,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Incident summarizer</t>
+          <t>Spend optimization agent</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5.6</v>
+        <v>1.2</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -610,7 +610,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cash forecasting copilot</t>
+          <t>Audit evidence assembler</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -618,12 +618,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>18m</t>
+          <t>6m</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -635,15 +635,15 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Liquidity scenario modeler</t>
+          <t>Audit evidence assembler</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2.7</v>
+        <v>7.3</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>18m</t>
+          <t>12m</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -660,11 +660,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Forecast variance explainer</t>
+          <t>FX hedge advisor</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -685,11 +685,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Payment anomaly detection</t>
+          <t>Reporting rationalization agent</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -710,20 +710,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bank fee analyzer</t>
+          <t>Reporting rationalization agent</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>7.9</v>
+        <v>4.3</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>12m</t>
+          <t>18m</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -735,15 +735,15 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Audit evidence assembler</t>
+          <t>Reporting rationalization agent</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>6m</t>
+          <t>12m</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -760,15 +760,15 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Vendor scorecard agent</t>
+          <t>Spend optimization agent</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>12m</t>
+          <t>18m</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -785,20 +785,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>FX hedge advisor</t>
+          <t>Spend optimization agent</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>18m</t>
+          <t>12m</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -810,11 +810,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Close acceleration assistant</t>
+          <t>Cash forecasting copilot</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>7.2</v>
+        <v>4</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
